--- a/output/pdf_financials_xlsx/RAK.xlsx
+++ b/output/pdf_financials_xlsx/RAK.xlsx
@@ -1002,16 +1002,16 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.009285</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.089891</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.076623</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.191358</v>
       </c>
     </row>
     <row r="13">
@@ -1904,16 +1904,16 @@
         <v>-0.221818</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.678387</v>
+        <v>-1.687672</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-5.885489</v>
+        <v>-5.97538</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.777521</v>
+        <v>-3.854144</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-6.705365</v>
+        <v>-6.896723</v>
       </c>
     </row>
     <row r="28">
@@ -2008,16 +2008,16 @@
         <v>-0.221818</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.678387</v>
+        <v>-1.687672</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.885489</v>
+        <v>-5.97538</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.777521</v>
+        <v>-3.854144</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.705365</v>
+        <v>-6.896723</v>
       </c>
     </row>
     <row r="30">
@@ -2250,49 +2250,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.999514</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.629217</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.148169</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.046819</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.077552</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.031254</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.245217</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.092267</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.013979</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.02056</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.025795</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.427903</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.181671</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.264346</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>9.683401</v>
       </c>
     </row>
     <row r="35">
@@ -2354,49 +2354,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.999514</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.629217</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.148169</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.046819</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.077552</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.031254</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.245217</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.092267</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.013979</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.02056</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.025795</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>4.427903</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.181671</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>3.264346</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>9.683401</v>
       </c>
     </row>
     <row r="37">
@@ -2978,49 +2978,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.604636</v>
+        <v>0.605122</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.073515</v>
+        <v>0.444298</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.173069</v>
+        <v>0.0249</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.059064</v>
+        <v>0.012245</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.083887</v>
+        <v>0.006335</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.036537</v>
+        <v>0.005283</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.250862</v>
+        <v>0.005645</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.097012</v>
+        <v>0.004745</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.01935</v>
+        <v>0.005371</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.036563</v>
+        <v>0.016003</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.035036</v>
+        <v>0.009240999999999999</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.442533</v>
+        <v>0.01463</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.629932</v>
+        <v>0.448261</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.337018</v>
+        <v>0.072672</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>9.892898000000001</v>
+        <v>0.209497</v>
       </c>
     </row>
     <row r="49">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
@@ -16871,7 +16871,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -23104,7 +23108,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">

--- a/output/pdf_financials_xlsx/RAK.xlsx
+++ b/output/pdf_financials_xlsx/RAK.xlsx
@@ -745,13 +745,13 @@
         <v>0.148</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.491215</v>
+        <v>0.521215</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.544303</v>
+        <v>0.571803</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.893103</v>
+        <v>0.940603</v>
       </c>
     </row>
     <row r="8">
@@ -1235,7 +1235,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -20242,7 +20242,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -22181,7 +22185,11 @@
           <t>Directors’ fees (Note 15)</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -39845,7 +39853,11 @@
           <t>Deferred income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -41659,7 +41671,11 @@
           <t>Deferred income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
